--- a/Progress/coding/Global_tracker.XLSX
+++ b/Progress/coding/Global_tracker.XLSX
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I606"/>
+  <dimension ref="A1:I610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.862142857142857" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
@@ -981,11 +981,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Advanced Graph</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="2" t="n"/>
+          <t>Graph / Bridges / Tarjan's Low-Link (Undirected)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>06sep2026</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
@@ -15390,6 +15396,138 @@
       <c r="G606" s="6" t="n"/>
       <c r="H606" s="6" t="n"/>
       <c r="I606" s="6" t="n"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="6" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B607" s="6" t="inlineStr">
+        <is>
+          <t>1095 - Find in Mountain Array</t>
+        </is>
+      </c>
+      <c r="C607" s="6" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D607" s="6" t="inlineStr">
+        <is>
+          <t>Binary Search / Interactive / Bitonic Array</t>
+        </is>
+      </c>
+      <c r="E607" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F607" s="6" t="inlineStr">
+        <is>
+          <t>25aug2026</t>
+        </is>
+      </c>
+      <c r="G607" s="6" t="n"/>
+      <c r="H607" s="6" t="n"/>
+      <c r="I607" s="6" t="n"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="6" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B608" s="6" t="inlineStr">
+        <is>
+          <t>587 - Erect the Fence</t>
+        </is>
+      </c>
+      <c r="C608" s="6" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D608" s="6" t="inlineStr">
+        <is>
+          <t>Geometry / Convex Hull / Andrew's Monotone Chain</t>
+        </is>
+      </c>
+      <c r="E608" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F608" s="6" t="inlineStr">
+        <is>
+          <t>28aug2026</t>
+        </is>
+      </c>
+      <c r="G608" s="6" t="n"/>
+      <c r="H608" s="6" t="n"/>
+      <c r="I608" s="6" t="n"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="6" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B609" s="6" t="inlineStr">
+        <is>
+          <t>2097 - Valid Arrangement of Pairs</t>
+        </is>
+      </c>
+      <c r="C609" s="6" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D609" s="6" t="inlineStr">
+        <is>
+          <t>Graph / Eulerian Path / Hierholzer's Algorithm</t>
+        </is>
+      </c>
+      <c r="E609" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F609" s="6" t="inlineStr">
+        <is>
+          <t>29aug2026</t>
+        </is>
+      </c>
+      <c r="G609" s="6" t="n"/>
+      <c r="H609" s="6" t="n"/>
+      <c r="I609" s="6" t="n"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="6" t="inlineStr">
+        <is>
+          <t>leetcode</t>
+        </is>
+      </c>
+      <c r="B610" s="6" t="inlineStr">
+        <is>
+          <t>2360 - Longest Cycle in a Graph</t>
+        </is>
+      </c>
+      <c r="C610" s="6" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="D610" s="6" t="inlineStr">
+        <is>
+          <t>Graph / Functional Graph / Cycle Detection (Simplified Tarjan)</t>
+        </is>
+      </c>
+      <c r="E610" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F610" s="6" t="inlineStr">
+        <is>
+          <t>05sep2026</t>
+        </is>
+      </c>
+      <c r="G610" s="6" t="n"/>
+      <c r="H610" s="6" t="n"/>
+      <c r="I610" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Progress/coding/Global_tracker.XLSX
+++ b/Progress/coding/Global_tracker.XLSX
@@ -1206,8 +1206,14 @@
           <t>Bitmask DP / Bits | Bitmask + subset enumeration</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="2" t="n"/>
+      <c r="E26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>21oct2026</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
@@ -1858,8 +1864,14 @@
           <t>Recursion</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n"/>
-      <c r="F50" s="2" t="n"/>
+      <c r="E50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>07oct2026</t>
+        </is>
+      </c>
       <c r="G50" s="2" t="n"/>
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="n"/>
@@ -1885,8 +1897,14 @@
           <t>Binary Search</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="2" t="n"/>
+      <c r="E51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>21oct2026</t>
+        </is>
+      </c>
       <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="n"/>
@@ -2074,8 +2092,14 @@
           <t>Monotonic Stack / DP | Monotonic stack + DP</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="2" t="n"/>
+      <c r="E58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>21oct2026</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="n"/>
